--- a/tests/workbooktests/workbooks/test_payoffs.xlsx
+++ b/tests/workbooktests/workbooks/test_payoffs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C327E0EE-C683-4486-B487-1499ED40F97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177503D4-40C4-41E2-810C-38A8E48611D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="-17900" windowWidth="23040" windowHeight="14790" xr2:uid="{FDFCF6E7-3EF4-4492-A3D0-D2FF7BDEAE05}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{FDFCF6E7-3EF4-4492-A3D0-D2FF7BDEAE05}"/>
   </bookViews>
   <sheets>
     <sheet name="Payoffs" sheetId="1" r:id="rId1"/>
@@ -542,156 +542,156 @@
       <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlPlainVanillaPayoff(B1,$B$3)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R8C2PlainVanillaPayoff,A</v>
-      </c>
-      <c r="C8" t="str" cm="1">
-        <f t="array" ref="C8">_xll.qlTypePayoffOptionType(B8)</f>
-        <v>CALL</v>
-      </c>
-      <c r="D8" cm="1">
-        <f t="array" ref="D8">_xll.qlStrikedTypePayoffStrike(B8)</f>
-        <v>100</v>
-      </c>
-      <c r="E8" cm="1">
-        <f t="array" ref="E8">_xll.qlPayoffValue(B8,B3+1)</f>
-        <v>1</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlPlainVanillaPayoff(B1,$B$3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" t="e" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_xll.qlTypePayoffOptionType(B8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D8" t="e" cm="1">
+        <f t="array" aca="1" ref="D8" ca="1">_xll.qlStrikedTypePayoffStrike(B8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E8" t="e" cm="1">
+        <f t="array" aca="1" ref="E8" ca="1">_xll.qlPayoffValue(B8,B3+1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" t="str" cm="1">
-        <f t="array" ref="B9">_xll.qlPlainVanillaPayoff(B2,$B$3)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R9C2PlainVanillaPayoff,A</v>
-      </c>
-      <c r="C9" t="str" cm="1">
-        <f t="array" ref="C9">_xll.qlTypePayoffOptionType(B9)</f>
-        <v>PUT</v>
-      </c>
-      <c r="D9" cm="1">
-        <f t="array" ref="D9">_xll.qlStrikedTypePayoffStrike(B9)</f>
-        <v>100</v>
-      </c>
-      <c r="E9" cm="1">
-        <f t="array" ref="E9">_xll.qlPayoffValue(B9,B3-1)</f>
-        <v>1</v>
+      <c r="B9" t="e" cm="1">
+        <f t="array" aca="1" ref="B9" ca="1">_xll.qlPlainVanillaPayoff(B2,$B$3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C9" t="e" cm="1">
+        <f t="array" aca="1" ref="C9" ca="1">_xll.qlTypePayoffOptionType(B9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D9" t="e" cm="1">
+        <f t="array" aca="1" ref="D9" ca="1">_xll.qlStrikedTypePayoffStrike(B9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E9" t="e" cm="1">
+        <f t="array" aca="1" ref="E9" ca="1">_xll.qlPayoffValue(B9,B3-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" t="str" cm="1">
-        <f t="array" ref="B11">_xll.qlPercentageStrikePayoff(B1,B4)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R11C2PercentageStrikePayoff,A</v>
-      </c>
-      <c r="C11" t="str" cm="1">
-        <f t="array" ref="C11">_xll.qlTypePayoffOptionType(B11)</f>
-        <v>CALL</v>
-      </c>
-      <c r="D11" cm="1">
-        <f t="array" ref="D11">_xll.qlStrikedTypePayoffStrike(B11)</f>
-        <v>0.8</v>
-      </c>
-      <c r="E11" cm="1">
-        <f t="array" ref="E11">_xll.qlPayoffValue(B11,B3)</f>
-        <v>19.999999999999996</v>
+      <c r="B11" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlPercentageStrikePayoff(B1,B4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" t="e" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">_xll.qlTypePayoffOptionType(B11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" t="e" cm="1">
+        <f t="array" aca="1" ref="D11" ca="1">_xll.qlStrikedTypePayoffStrike(B11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" t="e" cm="1">
+        <f t="array" aca="1" ref="E11" ca="1">_xll.qlPayoffValue(B11,B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlPercentageStrikePayoff(B2,B4)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R12C2PercentageStrikePayoff,A</v>
-      </c>
-      <c r="C12" t="str" cm="1">
-        <f t="array" ref="C12">_xll.qlTypePayoffOptionType(B12)</f>
-        <v>PUT</v>
-      </c>
-      <c r="D12" cm="1">
-        <f t="array" ref="D12">_xll.qlStrikedTypePayoffStrike(B12)</f>
-        <v>0.8</v>
-      </c>
-      <c r="E12" cm="1">
-        <f t="array" ref="E12">_xll.qlPayoffValue(B12,B3-2)</f>
-        <v>0</v>
+      <c r="B12" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlPercentageStrikePayoff(B2,B4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" t="e" cm="1">
+        <f t="array" aca="1" ref="C12" ca="1">_xll.qlTypePayoffOptionType(B12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D12" t="e" cm="1">
+        <f t="array" aca="1" ref="D12" ca="1">_xll.qlStrikedTypePayoffStrike(B12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E12" t="e" cm="1">
+        <f t="array" aca="1" ref="E12" ca="1">_xll.qlPayoffValue(B12,B3-2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" t="str" cm="1">
-        <f t="array" ref="B14">_xll.qlCashOrNothingPayoff(B1,B3,B5)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R14C2CashOrNothingPayoff,A</v>
-      </c>
-      <c r="C14" t="str" cm="1">
-        <f t="array" ref="C14">_xll.qlTypePayoffOptionType(B14)</f>
-        <v>CALL</v>
-      </c>
-      <c r="D14" cm="1">
-        <f t="array" ref="D14">_xll.qlStrikedTypePayoffStrike(B14)</f>
-        <v>100</v>
-      </c>
-      <c r="E14" cm="1">
-        <f t="array" ref="E14">_xll.qlPayoffValue(B14,D14+1)</f>
-        <v>20</v>
+      <c r="B14" t="e" cm="1">
+        <f t="array" aca="1" ref="B14" ca="1">_xll.qlCashOrNothingPayoff(B1,B3,B5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" t="e" cm="1">
+        <f t="array" aca="1" ref="C14" ca="1">_xll.qlTypePayoffOptionType(B14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" t="e" cm="1">
+        <f t="array" aca="1" ref="D14" ca="1">_xll.qlStrikedTypePayoffStrike(B14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" t="e" cm="1">
+        <f t="array" aca="1" ref="E14" ca="1">_xll.qlPayoffValue(B14,D14+1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" t="str" cm="1">
-        <f t="array" ref="B15">_xll.qlCashOrNothingPayoff(B2,B3,B5)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R15C2CashOrNothingPayoff,A</v>
-      </c>
-      <c r="C15" t="str" cm="1">
-        <f t="array" ref="C15">_xll.qlTypePayoffOptionType(B15)</f>
-        <v>PUT</v>
-      </c>
-      <c r="D15" cm="1">
-        <f t="array" ref="D15">_xll.qlStrikedTypePayoffStrike(B15)</f>
-        <v>100</v>
-      </c>
-      <c r="E15" cm="1">
-        <f t="array" ref="E15">_xll.qlPayoffValue(B15,D15-1)</f>
-        <v>20</v>
+      <c r="B15" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlCashOrNothingPayoff(B2,B3,B5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" t="e" cm="1">
+        <f t="array" aca="1" ref="C15" ca="1">_xll.qlTypePayoffOptionType(B15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D15" t="e" cm="1">
+        <f t="array" aca="1" ref="D15" ca="1">_xll.qlStrikedTypePayoffStrike(B15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" t="e" cm="1">
+        <f t="array" aca="1" ref="E15" ca="1">_xll.qlPayoffValue(B15,D15-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>10</v>
       </c>
-      <c r="B17" t="str" cm="1">
-        <f t="array" ref="B17">_xll.qlAssetOrNothingPayoff(B1,B3)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R17C2AssetOrNothingPayoff,A</v>
-      </c>
-      <c r="C17" t="str" cm="1">
-        <f t="array" ref="C17">_xll.qlTypePayoffOptionType(B17)</f>
-        <v>CALL</v>
-      </c>
-      <c r="D17" cm="1">
-        <f t="array" ref="D17">_xll.qlStrikedTypePayoffStrike(B17)</f>
-        <v>100</v>
-      </c>
-      <c r="E17" cm="1">
-        <f t="array" ref="E17">_xll.qlPayoffValue(B17,D17+1)</f>
-        <v>101</v>
+      <c r="B17" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlAssetOrNothingPayoff(B1,B3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" t="e" cm="1">
+        <f t="array" aca="1" ref="C17" ca="1">_xll.qlTypePayoffOptionType(B17)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D17" t="e" cm="1">
+        <f t="array" aca="1" ref="D17" ca="1">_xll.qlStrikedTypePayoffStrike(B17)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E17" t="e" cm="1">
+        <f t="array" aca="1" ref="E17" ca="1">_xll.qlPayoffValue(B17,D17+1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B18" t="str" cm="1">
-        <f t="array" ref="B18">_xll.qlAssetOrNothingPayoff(B2,B3)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R18C2AssetOrNothingPayoff,A</v>
-      </c>
-      <c r="C18" t="str" cm="1">
-        <f t="array" ref="C18">_xll.qlTypePayoffOptionType(B18)</f>
-        <v>PUT</v>
-      </c>
-      <c r="D18" cm="1">
-        <f t="array" ref="D18">_xll.qlStrikedTypePayoffStrike(B18)</f>
-        <v>100</v>
-      </c>
-      <c r="E18" cm="1">
-        <f t="array" ref="E18">_xll.qlPayoffValue(B18,D18-1)</f>
-        <v>99</v>
+      <c r="B18" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlAssetOrNothingPayoff(B2,B3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C18" t="e" cm="1">
+        <f t="array" aca="1" ref="C18" ca="1">_xll.qlTypePayoffOptionType(B18)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D18" t="e" cm="1">
+        <f t="array" aca="1" ref="D18" ca="1">_xll.qlStrikedTypePayoffStrike(B18)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E18" t="e" cm="1">
+        <f t="array" aca="1" ref="E18" ca="1">_xll.qlPayoffValue(B18,D18-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -714,39 +714,39 @@
       <c r="A23" t="s">
         <v>12</v>
       </c>
-      <c r="B23" t="str" cm="1">
-        <f t="array" ref="B23">_xll.qlSuperSharePayoff(B1,B20,B21)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R23C2SuperSharePayoff,A</v>
-      </c>
-      <c r="C23" t="str" cm="1">
-        <f t="array" ref="C23">_xll.qlTypePayoffOptionType(B23)</f>
-        <v>CALL</v>
-      </c>
-      <c r="D23" cm="1">
-        <f t="array" ref="D23">_xll.qlStrikedTypePayoffStrike(B23)</f>
-        <v>1</v>
-      </c>
-      <c r="E23" cm="1">
-        <f t="array" ref="E23">_xll.qlPayoffValue(B23,B20-1)</f>
-        <v>20</v>
+      <c r="B23" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlSuperSharePayoff(B1,B20,B21)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C23" t="e" cm="1">
+        <f t="array" aca="1" ref="C23" ca="1">_xll.qlTypePayoffOptionType(B23)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D23" t="e" cm="1">
+        <f t="array" aca="1" ref="D23" ca="1">_xll.qlStrikedTypePayoffStrike(B23)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E23" t="e" cm="1">
+        <f t="array" aca="1" ref="E23" ca="1">_xll.qlPayoffValue(B23,B20-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B24" t="str" cm="1">
-        <f t="array" ref="B24">_xll.qlSuperSharePayoff(B2,B20,B21)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R24C2SuperSharePayoff,A</v>
-      </c>
-      <c r="C24" t="str" cm="1">
-        <f t="array" ref="C24">_xll.qlTypePayoffOptionType(B24)</f>
-        <v>CALL</v>
-      </c>
-      <c r="D24" cm="1">
-        <f t="array" ref="D24">_xll.qlStrikedTypePayoffStrike(B24)</f>
-        <v>-1</v>
-      </c>
-      <c r="E24" cm="1">
-        <f t="array" ref="E24">_xll.qlPayoffValue(B24,B21-1)</f>
-        <v>20</v>
+      <c r="B24" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlSuperSharePayoff(B2,B20,B21)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C24" t="e" cm="1">
+        <f t="array" aca="1" ref="C24" ca="1">_xll.qlTypePayoffOptionType(B24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D24" t="e" cm="1">
+        <f t="array" aca="1" ref="D24" ca="1">_xll.qlStrikedTypePayoffStrike(B24)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E24" t="e" cm="1">
+        <f t="array" aca="1" ref="E24" ca="1">_xll.qlPayoffValue(B24,B21-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -769,78 +769,78 @@
       <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="str" cm="1">
-        <f t="array" ref="B28">_xll.qlGapPayoff(B1,B26,B27)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R28C2GapPayoff,A</v>
-      </c>
-      <c r="C28" t="str" cm="1">
-        <f t="array" ref="C28">_xll.qlTypePayoffOptionType(B28)</f>
-        <v>CALL</v>
-      </c>
-      <c r="D28" cm="1">
-        <f t="array" ref="D28">_xll.qlStrikedTypePayoffStrike(B28)</f>
-        <v>120</v>
-      </c>
-      <c r="E28" cm="1">
-        <f t="array" ref="E28">_xll.qlPayoffValue(B28,B27+21)</f>
-        <v>21</v>
+      <c r="B28" t="e" cm="1">
+        <f t="array" aca="1" ref="B28" ca="1">_xll.qlGapPayoff(B1,B26,B27)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C28" t="e" cm="1">
+        <f t="array" aca="1" ref="C28" ca="1">_xll.qlTypePayoffOptionType(B28)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D28" t="e" cm="1">
+        <f t="array" aca="1" ref="D28" ca="1">_xll.qlStrikedTypePayoffStrike(B28)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E28" t="e" cm="1">
+        <f t="array" aca="1" ref="E28" ca="1">_xll.qlPayoffValue(B28,B27+21)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B29" t="str" cm="1">
-        <f t="array" ref="B29">_xll.qlGapPayoff(B2,B26,B27)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R29C2GapPayoff,A</v>
-      </c>
-      <c r="C29" t="str" cm="1">
-        <f t="array" ref="C29">_xll.qlTypePayoffOptionType(B29)</f>
-        <v>PUT</v>
-      </c>
-      <c r="D29" cm="1">
-        <f t="array" ref="D29">_xll.qlStrikedTypePayoffStrike(B29)</f>
-        <v>120</v>
-      </c>
-      <c r="E29" cm="1">
-        <f t="array" ref="E29">_xll.qlPayoffValue(B29,B27-1)</f>
-        <v>1</v>
+      <c r="B29" t="e" cm="1">
+        <f t="array" aca="1" ref="B29" ca="1">_xll.qlGapPayoff(B2,B26,B27)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C29" t="e" cm="1">
+        <f t="array" aca="1" ref="C29" ca="1">_xll.qlTypePayoffOptionType(B29)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D29" t="e" cm="1">
+        <f t="array" aca="1" ref="D29" ca="1">_xll.qlStrikedTypePayoffStrike(B29)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E29" t="e" cm="1">
+        <f t="array" aca="1" ref="E29" ca="1">_xll.qlPayoffValue(B29,B27-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>16</v>
       </c>
-      <c r="B31" t="str" cm="1">
-        <f t="array" ref="B31">_xll.qlVanillaForwardPayoff(B1,B3)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R31C2VanillaForwardPayoff,A</v>
-      </c>
-      <c r="C31" t="str" cm="1">
-        <f t="array" ref="C31">_xll.qlTypePayoffOptionType(B31)</f>
-        <v>CALL</v>
-      </c>
-      <c r="D31" cm="1">
-        <f t="array" ref="D31">_xll.qlStrikedTypePayoffStrike(B31)</f>
-        <v>100</v>
-      </c>
-      <c r="E31" cm="1">
-        <f t="array" ref="E31">_xll.qlPayoffValue(B31,D31+1)</f>
-        <v>1</v>
+      <c r="B31" t="e" cm="1">
+        <f t="array" aca="1" ref="B31" ca="1">_xll.qlVanillaForwardPayoff(B1,B3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C31" t="e" cm="1">
+        <f t="array" aca="1" ref="C31" ca="1">_xll.qlTypePayoffOptionType(B31)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D31" t="e" cm="1">
+        <f t="array" aca="1" ref="D31" ca="1">_xll.qlStrikedTypePayoffStrike(B31)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E31" t="e" cm="1">
+        <f t="array" aca="1" ref="E31" ca="1">_xll.qlPayoffValue(B31,D31+1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B32" t="str" cm="1">
-        <f t="array" ref="B32">_xll.qlVanillaForwardPayoff(B2,B3)</f>
-        <v>⚡[test_payoffs.xlsx]Payoffs!R32C2VanillaForwardPayoff,A</v>
-      </c>
-      <c r="C32" t="str" cm="1">
-        <f t="array" ref="C32">_xll.qlTypePayoffOptionType(B32)</f>
-        <v>PUT</v>
-      </c>
-      <c r="D32" cm="1">
-        <f t="array" ref="D32">_xll.qlStrikedTypePayoffStrike(B32)</f>
-        <v>100</v>
-      </c>
-      <c r="E32" cm="1">
-        <f t="array" ref="E32">_xll.qlPayoffValue(B32,D32-1)</f>
-        <v>1</v>
+      <c r="B32" t="e" cm="1">
+        <f t="array" aca="1" ref="B32" ca="1">_xll.qlVanillaForwardPayoff(B2,B3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C32" t="e" cm="1">
+        <f t="array" aca="1" ref="C32" ca="1">_xll.qlTypePayoffOptionType(B32)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D32" t="e" cm="1">
+        <f t="array" aca="1" ref="D32" ca="1">_xll.qlStrikedTypePayoffStrike(B32)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E32" t="e" cm="1">
+        <f t="array" aca="1" ref="E32" ca="1">_xll.qlPayoffValue(B32,D32-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
